--- a/low_risk_results.xlsx
+++ b/low_risk_results.xlsx
@@ -828,15 +828,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>416005759</t>
+          <t>916001226</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Benton County</t>
+          <t>City of Aberdeen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>D:\Documents\Profesh\Forward Edge AI\Treasury AI\single-finding-fix\mdl-backend-demo\outputs\MDL-Benton_County-416005759-2023.docx</t>
+          <t>D:\Documents\Profesh\Forward Edge AI\Treasury AI\single-finding-fix\mdl-backend-demo\outputs\MDL-City_of_Aberdeen-916001226-2021.docx</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>http://localhost:8000/local/mdl/2023/MDL-Benton_County-416005759-2023.docx</t>
+          <t>http://localhost:8000/local/mdl/2021/MDL-City_of_Aberdeen-916001226-2021.docx</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1324,15 +1324,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>416005772</t>
+          <t>856000099</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chisago County</t>
+          <t>City of Alamogordo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>D:\Documents\Profesh\Forward Edge AI\Treasury AI\single-finding-fix\mdl-backend-demo\outputs\MDL-Chisago_County-416005772-2024.docx</t>
+          <t>D:\Documents\Profesh\Forward Edge AI\Treasury AI\single-finding-fix\mdl-backend-demo\outputs\MDL-City_of_Alamogordo-856000099-2023.docx</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>http://localhost:8000/local/mdl/2024/MDL-Chisago_County-416005772-2024.docx</t>
+          <t>http://localhost:8000/local/mdl/2023/MDL-City_of_Alamogordo-856000099-2023.docx</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
